--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE5620C-CC95-4E52-B0FF-B098D965BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E6BD4C-EF2A-4346-B4BE-57C1AA0DA7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -249,13 +249,20 @@
   <si>
     <t>very bad day</t>
   </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>very good day</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -359,7 +366,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -382,11 +389,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -427,9 +445,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -913,74 +937,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12600475</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1901,180 +1925,372 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>50</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>910</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>320</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>50</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>430</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>1010</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>240</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>50</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>50</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>500</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>70</v>
+      </c>
+      <c r="E28" s="14">
+        <v>80</v>
+      </c>
+      <c r="F28" s="14">
+        <v>400</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="14">
+        <v>80</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>80</v>
+      </c>
+      <c r="E29" s="14">
+        <v>40</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>200</v>
+      </c>
+      <c r="C30" s="14">
+        <v>50</v>
+      </c>
+      <c r="D30" s="14">
+        <v>60</v>
+      </c>
+      <c r="E30" s="14">
+        <v>80</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>90</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>90</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="22">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>400</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
@@ -10209,10 +10425,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
@@ -10221,8 +10433,12 @@
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K29 K31:K401 A32" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E6BD4C-EF2A-4346-B4BE-57C1AA0DA7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7F6B91-46C2-4148-B6E4-8780D351A151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,6 +255,9 @@
   <si>
     <t>very good day</t>
   </si>
+  <si>
+    <t>enjoy full day</t>
+  </si>
 </sst>
 </file>
 
@@ -262,7 +265,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="[$-14009]yyyy/mm/dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -448,12 +451,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,74 +940,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12600475</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -2247,7 +2250,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="22">
+      <c r="A32" s="19">
         <v>46277</v>
       </c>
       <c r="B32" s="14">
@@ -2269,15 +2272,15 @@
         <v>0</v>
       </c>
       <c r="H32" s="14">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>400</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>1040</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>66</v>
@@ -2293,51 +2296,101 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>400</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>0</v>
+      </c>
+      <c r="E33" s="14">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>50</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>990</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>50</v>
+      </c>
+      <c r="D34" s="14">
+        <v>200</v>
+      </c>
+      <c r="E34" s="14">
+        <v>50</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13">
+        <v>46280</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7F6B91-46C2-4148-B6E4-8780D351A151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5441084A-B6ED-421E-ACF1-F4A8C0014B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>enjoy full day</t>
+  </si>
+  <si>
+    <t>it’s a good day</t>
   </si>
 </sst>
 </file>
@@ -2391,69 +2394,139 @@
       <c r="A35" s="13">
         <v>46280</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>240</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>80</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>400</v>
+      </c>
+      <c r="G35" s="14">
+        <v>8</v>
+      </c>
+      <c r="H35" s="14">
+        <v>90</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>350</v>
+      </c>
+      <c r="C36" s="14">
+        <v>10</v>
+      </c>
+      <c r="D36" s="14">
+        <v>30</v>
+      </c>
+      <c r="E36" s="14">
+        <v>80</v>
+      </c>
+      <c r="F36" s="14">
+        <v>350</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="14">
+        <v>320</v>
+      </c>
+      <c r="C37" s="14">
+        <v>50</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>50</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>50</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5441084A-B6ED-421E-ACF1-F4A8C0014B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6AEABF-B08B-47E7-9700-E924C5E15D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>it’s a good day</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>I am stress becouse of CA</t>
   </si>
 </sst>
 </file>
@@ -2529,26 +2535,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>70</v>
+      </c>
+      <c r="D38" s="14">
+        <v>80</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>200</v>
+      </c>
+      <c r="G38" s="14">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14">
+        <v>60</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6AEABF-B08B-47E7-9700-E924C5E15D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF59237-7D7D-42B4-8112-4B5EBB03BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>I am stress becouse of CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no  class today </t>
   </si>
 </sst>
 </file>
@@ -2581,26 +2584,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>360</v>
+      </c>
+      <c r="E39" s="14">
+        <v>180</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>20</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF59237-7D7D-42B4-8112-4B5EBB03BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8C7396-8277-4370-9EE4-D5DF2D1747AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t xml:space="preserve">no  class today </t>
+  </si>
+  <si>
+    <t>CA today</t>
   </si>
 </sst>
 </file>
@@ -2630,48 +2633,96 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>50</v>
+      </c>
+      <c r="D40" s="14">
+        <v>0</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>1030</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>400</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>90</v>
+      </c>
+      <c r="E41" s="14">
+        <v>70</v>
+      </c>
+      <c r="F41" s="14">
+        <v>250</v>
+      </c>
+      <c r="G41" s="14">
+        <v>5</v>
+      </c>
+      <c r="H41" s="14">
+        <v>50</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599C5AF4-9F44-4531-96CD-22ECA95EEED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E8A129-7DBC-4991-92E2-054D6D99D84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -461,9 +461,6 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -479,6 +476,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,74 +962,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="22">
         <v>12600475</v>
       </c>
-      <c r="G2" s="17"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1076,48 +1076,48 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
+      <c r="A6" s="16">
         <v>46251</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="15">
         <v>420</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="15">
         <v>45</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="15">
         <v>120</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="15">
         <v>90</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="15">
         <v>300</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="15">
         <v>6</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="15">
         <v>30</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="17">
         <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1005</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="17">
         <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>435</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="M6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="N6" s="19" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2824,48 +2824,96 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="9">
+        <v>320</v>
+      </c>
+      <c r="C44" s="9">
+        <v>10</v>
+      </c>
+      <c r="D44" s="9">
+        <v>420</v>
+      </c>
+      <c r="E44" s="9">
+        <v>60</v>
+      </c>
+      <c r="F44" s="9">
+        <v>150</v>
+      </c>
+      <c r="G44" s="9">
+        <v>3</v>
+      </c>
+      <c r="H44" s="9">
+        <v>50</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+        <v>430</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="9">
+        <v>420</v>
+      </c>
+      <c r="C45" s="9">
+        <v>20</v>
+      </c>
+      <c r="D45" s="9">
+        <v>50</v>
+      </c>
+      <c r="E45" s="9">
+        <v>40</v>
+      </c>
+      <c r="F45" s="9">
+        <v>200</v>
+      </c>
+      <c r="G45" s="9">
+        <v>4</v>
+      </c>
+      <c r="H45" s="9">
+        <v>60</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>790</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
+        <v>650</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E8A129-7DBC-4991-92E2-054D6D99D84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3FE405-3763-4FF5-A879-480CAAA1371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2916,21 +2916,37 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="9">
+        <v>620</v>
+      </c>
+      <c r="C46" s="9">
+        <v>20</v>
+      </c>
+      <c r="D46" s="9">
+        <v>50</v>
+      </c>
+      <c r="E46" s="9">
+        <v>60</v>
+      </c>
+      <c r="F46" s="9">
+        <v>100</v>
+      </c>
+      <c r="G46" s="9">
+        <v>2</v>
+      </c>
+      <c r="H46" s="9">
+        <v>25</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>875</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>565</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
@@ -2938,21 +2954,37 @@
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="9">
+        <v>520</v>
+      </c>
+      <c r="C47" s="9">
+        <v>60</v>
+      </c>
+      <c r="D47" s="9">
+        <v>420</v>
+      </c>
+      <c r="E47" s="9">
+        <v>250</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>80</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>110</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
@@ -2960,21 +2992,37 @@
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+      <c r="A48" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B48" s="9">
+        <v>460</v>
+      </c>
+      <c r="C48" s="9">
+        <v>20</v>
+      </c>
+      <c r="D48" s="9">
+        <v>350</v>
+      </c>
+      <c r="E48" s="9">
+        <v>50</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>50</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>510</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
@@ -2982,21 +3030,37 @@
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
+      <c r="A49" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B49" s="9">
+        <v>380</v>
+      </c>
+      <c r="C49" s="9">
+        <v>10</v>
+      </c>
+      <c r="D49" s="9">
+        <v>420</v>
+      </c>
+      <c r="E49" s="9">
+        <v>60</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>80</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>490</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
@@ -3004,21 +3068,37 @@
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+      <c r="A50" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B50" s="9">
+        <v>480</v>
+      </c>
+      <c r="C50" s="9">
+        <v>30</v>
+      </c>
+      <c r="D50" s="9">
+        <v>600</v>
+      </c>
+      <c r="E50" s="9">
+        <v>90</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>30</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>210</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
@@ -3026,21 +3106,37 @@
       <c r="N50" s="12"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+      <c r="A51" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B51" s="9">
+        <v>650</v>
+      </c>
+      <c r="C51" s="9">
+        <v>50</v>
+      </c>
+      <c r="D51" s="9">
+        <v>360</v>
+      </c>
+      <c r="E51" s="9">
+        <v>200</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>60</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>120</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
@@ -3048,21 +3144,37 @@
       <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+      <c r="A52" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B52" s="9">
+        <v>340</v>
+      </c>
+      <c r="C52" s="9">
+        <v>60</v>
+      </c>
+      <c r="D52" s="9">
+        <v>360</v>
+      </c>
+      <c r="E52" s="9">
+        <v>60</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>40</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>580</v>
       </c>
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
@@ -3070,21 +3182,37 @@
       <c r="N52" s="12"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
+      <c r="A53" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B53" s="9">
+        <v>550</v>
+      </c>
+      <c r="C53" s="9">
+        <v>20</v>
+      </c>
+      <c r="D53" s="9">
+        <v>450</v>
+      </c>
+      <c r="E53" s="9">
+        <v>90</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>80</v>
+      </c>
+      <c r="I53" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>250</v>
       </c>
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3FE405-3763-4FF5-A879-480CAAA1371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAEBEFA-81D0-4F7D-9BC5-FB678C0B26D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2948,9 +2948,15 @@
         <f t="shared" si="1"/>
         <v>565</v>
       </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
+      <c r="K46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -2986,9 +2992,15 @@
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
+      <c r="K47" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -3024,9 +3036,15 @@
         <f t="shared" si="1"/>
         <v>510</v>
       </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
+      <c r="K48" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -3062,9 +3080,15 @@
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
+      <c r="K49" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -3100,9 +3124,15 @@
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
+      <c r="K50" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N50" s="12"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3138,9 +3168,15 @@
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
+      <c r="K51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -3176,9 +3212,15 @@
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
+      <c r="K52" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="N52" s="12"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3214,13 +3256,21 @@
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
+      <c r="K53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N53" s="12"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
+      <c r="A54" s="8">
+        <v>46298</v>
+      </c>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -3242,7 +3292,9 @@
       <c r="N54" s="12"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
+      <c r="A55" s="8">
+        <v>46299</v>
+      </c>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
@@ -3264,7 +3316,9 @@
       <c r="N55" s="12"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
+      <c r="A56" s="8">
+        <v>46300</v>
+      </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
@@ -3286,7 +3340,9 @@
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
+      <c r="A57" s="8">
+        <v>46301</v>
+      </c>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -3308,7 +3364,9 @@
       <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
+      <c r="A58" s="8">
+        <v>46302</v>
+      </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAEBEFA-81D0-4F7D-9BC5-FB678C0B26D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CB6099-8565-4D95-9CB7-B7968E6ED7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3388,7 +3388,9 @@
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
+      <c r="A59" s="8">
+        <v>46303</v>
+      </c>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
@@ -3410,7 +3412,9 @@
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
+      <c r="A60" s="8">
+        <v>46304</v>
+      </c>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
@@ -3432,7 +3436,9 @@
       <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
+      <c r="A61" s="8">
+        <v>46305</v>
+      </c>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
@@ -3454,7 +3460,9 @@
       <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
+      <c r="A62" s="8">
+        <v>46306</v>
+      </c>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
@@ -3476,7 +3484,9 @@
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
+      <c r="A63" s="8">
+        <v>46307</v>
+      </c>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CB6099-8565-4D95-9CB7-B7968E6ED7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1D9154-6E48-41FB-BFC3-104201791F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Making python project.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1164,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N7" s="12" t="s">
         <v>57</v>
@@ -1721,7 +1724,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="9">
         <v>400</v>
@@ -3271,240 +3274,440 @@
       <c r="A54" s="8">
         <v>46298</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
+      <c r="B54" s="9">
+        <v>360</v>
+      </c>
+      <c r="C54" s="9">
+        <v>20</v>
+      </c>
+      <c r="D54" s="9">
+        <v>600</v>
+      </c>
+      <c r="E54" s="9">
+        <v>62</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>20</v>
+      </c>
+      <c r="I54" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+        <v>1062</v>
+      </c>
+      <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N54" s="12"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>46299</v>
       </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
+      <c r="B55" s="9">
+        <v>420</v>
+      </c>
+      <c r="C55" s="9">
+        <v>60</v>
+      </c>
+      <c r="D55" s="9">
+        <v>420</v>
+      </c>
+      <c r="E55" s="9">
+        <v>80</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>30</v>
+      </c>
+      <c r="I55" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J55" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
+        <v>430</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N55" s="12"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>46300</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
+      <c r="B56" s="9">
+        <v>400</v>
+      </c>
+      <c r="C56" s="9">
+        <v>10</v>
+      </c>
+      <c r="D56" s="9">
+        <v>630</v>
+      </c>
+      <c r="E56" s="9">
+        <v>60</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>40</v>
+      </c>
+      <c r="I56" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J56" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
+        <v>300</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>46301</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
+      <c r="B57" s="9">
+        <v>420</v>
+      </c>
+      <c r="C57" s="9">
+        <v>50</v>
+      </c>
+      <c r="D57" s="9">
+        <v>500</v>
+      </c>
+      <c r="E57" s="9">
+        <v>70</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>62</v>
+      </c>
+      <c r="I57" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
+        <v>1102</v>
+      </c>
+      <c r="J57" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
+        <v>338</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>46302</v>
       </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+      <c r="B58" s="9">
+        <v>360</v>
+      </c>
+      <c r="C58" s="9">
+        <v>20</v>
+      </c>
+      <c r="D58" s="9">
+        <v>700</v>
+      </c>
+      <c r="E58" s="9">
+        <v>60</v>
+      </c>
+      <c r="F58" s="9">
+        <v>0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>40</v>
+      </c>
+      <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J58" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
+        <v>260</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>46303</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
+      <c r="B59" s="9">
+        <v>280</v>
+      </c>
+      <c r="C59" s="9">
+        <v>60</v>
+      </c>
+      <c r="D59" s="9">
+        <v>620</v>
+      </c>
+      <c r="E59" s="9">
+        <v>70</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>50</v>
+      </c>
+      <c r="I59" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
+        <v>360</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>46304</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
+      <c r="B60" s="9">
+        <v>450</v>
+      </c>
+      <c r="C60" s="9">
+        <v>50</v>
+      </c>
+      <c r="D60" s="9">
+        <v>360</v>
+      </c>
+      <c r="E60" s="9">
+        <v>320</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>30</v>
+      </c>
+      <c r="I60" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
+        <v>230</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>46305</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
+      <c r="B61" s="9">
+        <v>600</v>
+      </c>
+      <c r="C61" s="9">
+        <v>52</v>
+      </c>
+      <c r="D61" s="9">
+        <v>520</v>
+      </c>
+      <c r="E61" s="9">
+        <v>80</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>0</v>
+      </c>
+      <c r="I61" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
+        <v>1252</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
+        <v>188</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>46306</v>
       </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
+      <c r="B62" s="9">
+        <v>450</v>
+      </c>
+      <c r="C62" s="9">
+        <v>60</v>
+      </c>
+      <c r="D62" s="9">
+        <v>620</v>
+      </c>
+      <c r="E62" s="9">
+        <v>90</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>60</v>
+      </c>
+      <c r="I62" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J62" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
+        <v>160</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>46307</v>
       </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
+      <c r="B63" s="9">
+        <v>360</v>
+      </c>
+      <c r="C63" s="9">
+        <v>60</v>
+      </c>
+      <c r="D63" s="9">
+        <v>360</v>
+      </c>
+      <c r="E63" s="9">
+        <v>72</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>50</v>
+      </c>
+      <c r="I63" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+        <v>902</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
+        <v>538</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1D9154-6E48-41FB-BFC3-104201791F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83697FA-9C4B-42E6-B29D-C8A61ADA2F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3711,7 +3711,9 @@
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
+      <c r="A64" s="8">
+        <v>46308</v>
+      </c>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
@@ -3733,7 +3735,9 @@
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
+      <c r="A65" s="8">
+        <v>46309</v>
+      </c>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
@@ -3755,7 +3759,9 @@
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
+      <c r="A66" s="8">
+        <v>46310</v>
+      </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83697FA-9C4B-42E6-B29D-C8A61ADA2F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18990D7A-1D93-437D-ABE5-22BEE0754D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3783,7 +3783,9 @@
       <c r="N66" s="12"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
+      <c r="A67" s="8">
+        <v>46311</v>
+      </c>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
@@ -3805,7 +3807,9 @@
       <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
+      <c r="A68" s="8">
+        <v>46312</v>
+      </c>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
@@ -3827,7 +3831,9 @@
       <c r="N68" s="12"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
+      <c r="A69" s="8">
+        <v>46313</v>
+      </c>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -3849,7 +3855,9 @@
       <c r="N69" s="12"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
+      <c r="A70" s="8">
+        <v>46314</v>
+      </c>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
@@ -3871,7 +3879,9 @@
       <c r="N70" s="12"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
+      <c r="A71" s="8">
+        <v>46315</v>
+      </c>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18990D7A-1D93-437D-ABE5-22BEE0754D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE280E28-9DF7-497C-9C25-8DF98479C2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3714,214 +3714,396 @@
       <c r="A64" s="8">
         <v>46308</v>
       </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
+      <c r="B64" s="9">
+        <v>420</v>
+      </c>
+      <c r="C64" s="9">
+        <v>60</v>
+      </c>
+      <c r="D64" s="9">
+        <v>450</v>
+      </c>
+      <c r="E64" s="9">
+        <v>90</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>40</v>
+      </c>
+      <c r="I64" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
+        <v>380</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>46309</v>
       </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+      <c r="B65" s="9">
+        <v>320</v>
+      </c>
+      <c r="C65" s="9">
+        <v>50</v>
+      </c>
+      <c r="D65" s="9">
+        <v>520</v>
+      </c>
+      <c r="E65" s="9">
+        <v>60</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>60</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
+        <v>430</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>46310</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+      <c r="B66" s="9">
+        <v>500</v>
+      </c>
+      <c r="C66" s="9">
+        <v>60</v>
+      </c>
+      <c r="D66" s="9">
+        <v>360</v>
+      </c>
+      <c r="E66" s="9">
+        <v>50</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
+        <v>470</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N66" s="12"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>46311</v>
       </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+      <c r="B67" s="9">
+        <v>400</v>
+      </c>
+      <c r="C67" s="9">
+        <v>40</v>
+      </c>
+      <c r="D67" s="9">
+        <v>420</v>
+      </c>
+      <c r="E67" s="9">
+        <v>360</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>40</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
+        <v>180</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>46312</v>
       </c>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+      <c r="B68" s="9">
+        <v>450</v>
+      </c>
+      <c r="C68" s="9">
+        <v>30</v>
+      </c>
+      <c r="D68" s="9">
+        <v>560</v>
+      </c>
+      <c r="E68" s="9">
+        <v>40</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>50</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
+        <v>310</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="N68" s="12"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>46313</v>
       </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+      <c r="B69" s="9">
+        <v>360</v>
+      </c>
+      <c r="C69" s="9">
+        <v>60</v>
+      </c>
+      <c r="D69" s="9">
+        <v>600</v>
+      </c>
+      <c r="E69" s="9">
+        <v>90</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0</v>
+      </c>
+      <c r="G69" s="9">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9">
+        <v>50</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
+        <v>280</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="N69" s="12"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>46314</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+      <c r="B70" s="9">
+        <v>320</v>
+      </c>
+      <c r="C70" s="9">
+        <v>20</v>
+      </c>
+      <c r="D70" s="9">
+        <v>300</v>
+      </c>
+      <c r="E70" s="9">
+        <v>70</v>
+      </c>
+      <c r="F70" s="9">
+        <v>250</v>
+      </c>
+      <c r="G70" s="9">
+        <v>5</v>
+      </c>
+      <c r="H70" s="9">
+        <v>60</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
+        <v>420</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="N70" s="12"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>46315</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="B71" s="9">
+        <v>320</v>
+      </c>
+      <c r="C71" s="9">
+        <v>60</v>
+      </c>
+      <c r="D71" s="9">
+        <v>400</v>
+      </c>
+      <c r="E71" s="9">
+        <v>60</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>70</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>910</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
+        <v>530</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="A72" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B72" s="9">
+        <v>420</v>
+      </c>
+      <c r="C72" s="9">
+        <v>40</v>
+      </c>
+      <c r="D72" s="9">
+        <v>420</v>
+      </c>
+      <c r="E72" s="9">
+        <v>60</v>
+      </c>
+      <c r="F72" s="9">
+        <v>350</v>
+      </c>
+      <c r="G72" s="9">
+        <v>7</v>
+      </c>
+      <c r="H72" s="9">
+        <v>90</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
+        <v>60</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE280E28-9DF7-497C-9C25-8DF98479C2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2710DF-BA04-49E9-94BA-1A7D7CD1477E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4107,25 +4107,47 @@
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+      <c r="A73" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B73" s="9">
+        <v>520</v>
+      </c>
+      <c r="C73" s="9">
+        <v>40</v>
+      </c>
+      <c r="D73" s="9">
+        <v>360</v>
+      </c>
+      <c r="E73" s="9">
+        <v>50</v>
+      </c>
+      <c r="F73" s="9">
+        <v>150</v>
+      </c>
+      <c r="G73" s="9">
+        <v>3</v>
+      </c>
+      <c r="H73" s="9">
+        <v>70</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
+        <v>250</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2710DF-BA04-49E9-94BA-1A7D7CD1477E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D40164-4D7C-405B-86E5-5CFCCAD83A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4151,7 +4151,9 @@
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
+      <c r="A74" s="8">
+        <v>46318</v>
+      </c>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
@@ -4173,7 +4175,9 @@
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
+      <c r="A75" s="8">
+        <v>46319</v>
+      </c>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -4195,7 +4199,9 @@
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
+      <c r="A76" s="8">
+        <v>46320</v>
+      </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D40164-4D7C-405B-86E5-5CFCCAD83A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE01591-5C44-4A77-9E58-DC4CE1B678A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4154,94 +4154,176 @@
       <c r="A74" s="8">
         <v>46318</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+      <c r="B74" s="9">
+        <v>600</v>
+      </c>
+      <c r="C74" s="9">
+        <v>40</v>
+      </c>
+      <c r="D74" s="9">
+        <v>450</v>
+      </c>
+      <c r="E74" s="9">
+        <v>60</v>
+      </c>
+      <c r="F74" s="9">
+        <v>200</v>
+      </c>
+      <c r="G74" s="9">
+        <v>4</v>
+      </c>
+      <c r="H74" s="9">
+        <v>60</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>46319</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="B75" s="9">
+        <v>320</v>
+      </c>
+      <c r="C75" s="9">
+        <v>50</v>
+      </c>
+      <c r="D75" s="9">
+        <v>650</v>
+      </c>
+      <c r="E75" s="9">
+        <v>50</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>60</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
+        <v>310</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>46320</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="B76" s="9">
+        <v>360</v>
+      </c>
+      <c r="C76" s="9">
+        <v>50</v>
+      </c>
+      <c r="D76" s="9">
+        <v>40</v>
+      </c>
+      <c r="E76" s="9">
+        <v>90</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>0</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>540</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
+        <v>900</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="A77" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B77" s="9">
+        <v>520</v>
+      </c>
+      <c r="C77" s="9">
+        <v>40</v>
+      </c>
+      <c r="D77" s="9">
+        <v>60</v>
+      </c>
+      <c r="E77" s="9">
+        <v>70</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>690</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
+        <v>750</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE01591-5C44-4A77-9E58-DC4CE1B678A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750CCC53-D4CD-4ABF-AA0E-D806FB50F4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4327,7 +4327,9 @@
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
+      <c r="A78" s="8">
+        <v>46322</v>
+      </c>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
@@ -4349,7 +4351,9 @@
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
+      <c r="A79" s="8">
+        <v>46323</v>
+      </c>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750CCC53-D4CD-4ABF-AA0E-D806FB50F4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA34B373-A155-42A8-9000-64100D70DBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4375,7 +4375,9 @@
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
+      <c r="A80" s="8">
+        <v>46324</v>
+      </c>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA34B373-A155-42A8-9000-64100D70DBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0310077-DE68-4515-8626-C866C74178AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4330,94 +4330,176 @@
       <c r="A78" s="8">
         <v>46322</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="B78" s="9">
+        <v>350</v>
+      </c>
+      <c r="C78" s="9">
+        <v>10</v>
+      </c>
+      <c r="D78" s="9">
+        <v>90</v>
+      </c>
+      <c r="E78" s="9">
+        <v>50</v>
+      </c>
+      <c r="F78" s="9">
+        <v>400</v>
+      </c>
+      <c r="G78" s="9">
+        <v>8</v>
+      </c>
+      <c r="H78" s="9">
+        <v>50</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>46323</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="B79" s="9">
+        <v>360</v>
+      </c>
+      <c r="C79" s="9">
+        <v>0</v>
+      </c>
+      <c r="D79" s="9">
+        <v>60</v>
+      </c>
+      <c r="E79" s="9">
+        <v>40</v>
+      </c>
+      <c r="F79" s="9">
+        <v>350</v>
+      </c>
+      <c r="G79" s="9">
+        <v>7</v>
+      </c>
+      <c r="H79" s="9">
+        <v>40</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>850</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
+        <v>590</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>46324</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="B80" s="9">
+        <v>450</v>
+      </c>
+      <c r="C80" s="9">
+        <v>0</v>
+      </c>
+      <c r="D80" s="9">
+        <v>70</v>
+      </c>
+      <c r="E80" s="9">
+        <v>70</v>
+      </c>
+      <c r="F80" s="9">
+        <v>150</v>
+      </c>
+      <c r="G80" s="9">
+        <v>3</v>
+      </c>
+      <c r="H80" s="9">
+        <v>60</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
+        <v>640</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
+      <c r="A81" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B81" s="9">
+        <v>620</v>
+      </c>
+      <c r="C81" s="9">
+        <v>0</v>
+      </c>
+      <c r="D81" s="9">
+        <v>80</v>
+      </c>
+      <c r="E81" s="9">
+        <v>60</v>
+      </c>
+      <c r="F81" s="9">
+        <v>200</v>
+      </c>
+      <c r="G81" s="9">
+        <v>4</v>
+      </c>
+      <c r="H81" s="9">
+        <v>40</v>
+      </c>
+      <c r="I81" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J81" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
+        <v>440</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
